--- a/01_Reporting_Suite/Reports/2026-08-05/Replacement_Costs_GAP_LIST_2026-08-05.xlsx
+++ b/01_Reporting_Suite/Reports/2026-08-05/Replacement_Costs_GAP_LIST_2026-08-05.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -827,12 +827,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Forklift 5.0t Diesel (FK505)</t>
+          <t>Forklift Container Mast 3.5t Diesel</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16816-590743-0001</t>
+          <t>1312732</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -840,159 +840,159 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DGH Engineering</t>
+          <t>Veolia</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Forklift Container Mast 3.5t Diesel</t>
+          <t>Forklift Rough Terrain 2.5t 4WD Diesel</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1312732</t>
+          <t>1312654, 1312655</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Veolia</t>
+          <t>Cement Australia Holdings Pty Ltd, DGH Engineering</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Forklift Rough Terrain 2.5t 4WD Diesel</t>
+          <t>G-Size Large Oxy Trolley</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1312654, 1312655</t>
+          <t>OXYTROLLEYLARGE-0012</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd, DGH Engineering</t>
+          <t>DGH Engineering</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Fuel Trailer 1000L Double Bunded</t>
+          <t>Generator - 100kVA (Diesel)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1117098</t>
+          <t>1276457, 1276461</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Programmed</t>
+          <t>Veolia</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>G-Size Large Oxy Trolley</t>
+          <t>Generator - 160kVA (Diesel)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OXYTROLLEYLARGE-0012</t>
+          <t>1276549, 1276557</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DGH Engineering</t>
+          <t>Cement Australia Holdings Pty Ltd, Veolia</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Generator - 100kVA (Diesel)</t>
+          <t>Generator - 20kVA (Diesel)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1276457, 1276461, 1276462</t>
+          <t>1320990, 1320991</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd, Veolia</t>
+          <t>DGH Engineering, Veolia</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Generator - 160kVA (Diesel)</t>
+          <t>Generator - 30kVA (Diesel)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1276549, 1276557</t>
+          <t>1320977</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd, Veolia</t>
+          <t>Cement Australia Holdings Pty Ltd</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Generator - 20kVA (Diesel)</t>
+          <t>Generator - 60kVA (Diesel)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1320990, 1320991</t>
+          <t>1320825</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DGH Engineering, Veolia</t>
+          <t>DGH Engineering</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Generator - 30kVA (Diesel)</t>
+          <t>Knuckle Boom 130ft (39.5M) - Diesel</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1320977</t>
+          <t>1221712</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd</t>
+          <t>DGH Engineering</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Generator - 60kVA (Diesel)</t>
+          <t>Knuckle Boom 61ft (18.6M) - Diesel</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1320825</t>
+          <t>1312869</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1027,112 +1027,112 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Knuckle Boom 130ft (39.5M) - Diesel</t>
+          <t>Lifeguard 16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1221712</t>
+          <t>1200718, 1200726, 1200744, 1200747, 1206954, 1207008, 1207010, 1207017</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DGH Engineering</t>
+          <t>Cement Australia Holdings Pty Ltd, DGH Engineering, Sync Lift Engineering, Veoli</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Knuckle Boom 61ft (18.6M) - Diesel</t>
+          <t>Light Telescopic 4 Head LED 27000lm (3m) - Hybrid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1312869</t>
+          <t>1270837, 1270839</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DGH Engineering</t>
+          <t>Cement Australia Holdings Pty Ltd, Veolia</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lifeguard 16</t>
+          <t>Lighting Tower LED 170-240k Lumens Mine Spec</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1200718, 1200726, 1200744, 1200747, 1206954, 1207008, 1207010, 1207017</t>
+          <t>1229297, 1281595, 1295771, 1295773</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd, DGH Engineering, Sync Lift Engineering, Veoli</t>
+          <t>Cement Australia Holdings Pty Ltd, DGH Engineering</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Light Telescopic 4 Head LED 27000lm (3m) - Hybrid</t>
+          <t>Lighting Tower LED Cube Diesel</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1270837, 1270839</t>
+          <t>1226154</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd, Veolia</t>
+          <t>DGH Engineering</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lighting Tower LED 170-240k Lumens Mine Spec</t>
+          <t>Lighting Tower LED Metro</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1229297, 1281595, 1295771, 1295773</t>
+          <t>1276086, 1276093</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd, DGH Engineering</t>
+          <t>Cement Australia Holdings Pty Ltd, Xtreme Engineering</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Lighting Tower LED Cube Diesel</t>
+          <t>Lighting Tower POD Metro</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1226154</t>
+          <t>1219218</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1140,139 +1140,139 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DGH Engineering</t>
+          <t>High Risk Solutions</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lighting Tower LED Metro</t>
+          <t>Milwaukee 18 V 6 Ah Battery</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1276086, 1276093</t>
+          <t>BATMIL18V6A-0206, BATMIL18V6A-0423, BATMIL18V6A-0478, BATMIL18V6A-0555</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd, Xtreme Engineering</t>
+          <t>DGH Engineering, High Risk Solutions, Programmed, Veolia</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lighting Tower POD Metro</t>
+          <t>Milwaukee 2,500 lm Telescopic LED Battery Light - 2.10 m</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1219218</t>
+          <t>1269882, 1303385</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>High Risk Solutions</t>
+          <t>Programmed, Veolia</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Milwaukee 18 V 6 Ah Battery</t>
+          <t>Milwaukee 4,400 lm LED Battery Light</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BATMIL18V6A-0206, BATMIL18V6A-0423, BATMIL18V6A-0550, BATMIL18V6A-0555</t>
+          <t>1257961, 1257966</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DGH Engineering, Tasman Rope Access, Veolia</t>
+          <t>High Risk Solutions</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Milwaukee 4,400 lm LED Battery Light</t>
+          <t>Pallet Truck 1.8t Electric</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1257961, 1257965</t>
+          <t>1280585, 1280586, 1280591, 1280598, 1297566</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>High Risk Solutions, Programmed</t>
+          <t>Cement Australia Holdings Pty Ltd, Veolia</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Pallet Truck 1.8t Electric</t>
+          <t>Paramount Safety Bollard &amp; Bollard Bases 6KG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1280585, 1280586, 1280591, 1280598, 1297566</t>
+          <t>CEME9016-590836-0001, CEME9016-590836-0002, CEME9016-590836-0003, CEME9016-590836-0004, CEME9016-590836-0005, CEME9016-590836-0006, CEME9016-590836-0007, CEME9016-590836-0008, CEME9016-590836-0009, CEME9016-590836-0010, CEME9016-590836-0011, CEME9016-590836-0012, CEME9016-590836-0013, CEME9016-590836-0015, CEME9016-590836-0017, CEME9016-590836-0018, CEME9016-590836-0019, CEME9016-590836-0020, CEME9016-590836-0021, CEME9016-590836-0024</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd, Veolia</t>
+          <t>Cement Australia Holdings Pty Ltd, DGH Engineering, Dark Knight Engineering</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Paramount Safety Bollard &amp; Bollard Bases 6KG</t>
+          <t>Scissor Lift With Operator Protection 19ft (5.7m)  Electric</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CEME9016-590836-0001, CEME9016-590836-0002, CEME9016-590836-0003, CEME9016-590836-0004, CEME9016-590836-0005, CEME9016-590836-0006, CEME9016-590836-0007, CEME9016-590836-0008, CEME9016-590836-0009, CEME9016-590836-0010, CEME9016-590836-0011, CEME9016-590836-0012, CEME9016-590836-0013, CEME9016-590836-0015, CEME9016-590836-0017, CEME9016-590836-0018, CEME9016-590836-0019, CEME9016-590836-0020, CEME9016-590836-0021, CEME9016-590836-0024</t>
+          <t>1253744</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd, DGH Engineering, Dark Knight Engineering</t>
+          <t>Cement Australia Holdings Pty Ltd</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Scissor Lift With Operator Protection 19ft (5.7m)  Electric</t>
+          <t>Scissor Lift With Operator Protection 19ft (5.7m)  Electric - Greener Choice</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1253744</t>
+          <t>1280188</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -1280,19 +1280,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd</t>
+          <t>Veolia</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Scissor Lift With Operator Protection 19ft (5.7m)  Electric - Greener Choice</t>
+          <t>Scissor Lift With Operator Protection 32ft (9.7m)  Electric</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1280188</t>
+          <t>1247956</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -1300,39 +1300,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Veolia</t>
+          <t>Cement Australia Holdings Pty Ltd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Scissor Lift With Operator Protection 32ft (9.7m)  Electric</t>
+          <t>Toilet Portable - Fresh Water Flush</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1247956</t>
+          <t>1058029, 1127069</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd</t>
+          <t>Programmed</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Straight Boom Lift 32.3m (105ft) Diesel</t>
+          <t>Trailer Mounted Boom 10.2m Diesel/Electric</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1313105</t>
+          <t>1298793</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -1340,79 +1340,79 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Tasman Rope Access</t>
+          <t>High Risk Solutions</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Toilet Portable - Fresh Water Flush</t>
+          <t>Water Blaster - 3000 PSI Hot / Cold on Trailer (Diesel)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1058029, 1127069</t>
+          <t>1313742</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Programmed</t>
+          <t>Cement Australia Holdings Pty Ltd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Water Blaster - 3000 PSI Hot / Cold on Trailer (Diesel)</t>
+          <t>Welder - Motorised - Diesel - 600A Air Vantage</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1313742</t>
+          <t>1226045, 1235624, 1235626</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd</t>
+          <t>Cement Australia Holdings Pty Ltd, DGH Engineering</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Welder - Motorised - Diesel - 600A Air Vantage</t>
+          <t>Welder Diesel 500A</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>1226041, 1226045, 1235624, 1235626</t>
+          <t>1235657</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Cement Australia Holdings Pty Ltd, DGH Engineering</t>
+          <t>Veolia</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Welder Diesel 500A</t>
+          <t>Welding Air Vantage Diesel 500(HGA014)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1235657</t>
+          <t>16816-590535-0001</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -1420,19 +1420,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Veolia</t>
+          <t>DGH Engineering</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Welding Air Vantage Diesel 500(HGA014)</t>
+          <t>Welding Air Vantage Diesel 500(HGA032)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>16816-590535-0001</t>
+          <t>16816-590736-0001</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -1440,19 +1440,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>DGH Engineering</t>
+          <t>Veolia</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Welding Air Vantage Diesel 500(HGA032)</t>
+          <t>Welding Vantage Diesel 500(HGA009)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>16816-590736-0001</t>
+          <t>16816-590737-0001</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -1460,19 +1460,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Veolia</t>
+          <t>DGH Engineering</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Welding Vantage Diesel 500(HGA009)</t>
+          <t>Welding Vantage Diesel 500(HGA044)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>16816-590737-0001</t>
+          <t>16816-590738-0001</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -1480,19 +1480,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>DGH Engineering</t>
+          <t>Veolia</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Welding Vantage Diesel 500(HGA044)</t>
+          <t>Welding Vantage Diesel 580 (HGA047)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>16816-590738-0001</t>
+          <t>16816-590739-0001</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -1507,12 +1507,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Welding Vantage Diesel 580 (HGA047)</t>
+          <t>Welding Vantage Diesel 580(HGA035)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>16816-590739-0001</t>
+          <t>16816-590740-0001</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -1527,12 +1527,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Welding Vantage Diesel 580(HGA035)</t>
+          <t>Welding Vantage Diesel 580(HGA041</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16816-590740-0001</t>
+          <t>16816-590741-0001</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -1547,38 +1547,18 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Welding Vantage Diesel 580(HGA041</t>
+          <t>Welding Vantage Diesel 580(HGA042)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>16816-590741-0001</t>
+          <t>16816-590742-0001</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="inlineStr">
-        <is>
-          <t>Veolia</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Welding Vantage Diesel 580(HGA042)</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>16816-590742-0001</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" t="inlineStr">
         <is>
           <t>Veolia</t>
         </is>
